--- a/administration-des-ventes/assets/exercices-excel/bio-2.xlsx
+++ b/administration-des-ventes/assets/exercices-excel/bio-2.xlsx
@@ -1,39 +1,489 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nellydoucet\Documents\02. SECRETAIRE COMPTABLE\02. ADMINISTRATION DES VENTES\2023\01. ADMINISTRATION DES VENTES\SC2024\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9D383AA-420D-416B-A2D6-0E437774B251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{31AA7DA7-77DF-4F79-B56E-8A56121FEEEC}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Feuilles de calcul</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Feuil1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Nelly DOUCET</dc:creator>
+  <cp:lastModifiedBy>Nelly DOUCET</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2024-03-25T15:19:57Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2024-03-25T15:20:43Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
+<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <c r="D42" i="1" l="1"/>
+  <c r="U37" i="1"/>
+  <c r="V37" i="1" s="1"/>
+  <c r="H37" i="1"/>
+  <c r="I37" i="1" s="1"/>
+  <c r="U36" i="1"/>
+  <c r="V36" i="1" s="1"/>
+  <c r="H36" i="1"/>
+  <c r="I36" i="1" s="1"/>
+  <c r="U35" i="1"/>
+  <c r="V35" i="1" s="1"/>
+  <c r="I35" i="1"/>
+  <c r="V34" i="1"/>
+  <c r="U34" i="1"/>
+  <c r="H34" i="1"/>
+  <c r="I34" i="1" s="1"/>
+  <c r="I38" i="1" s="1"/>
+  <c r="V33" i="1"/>
+  <c r="U33" i="1"/>
+  <c r="I33" i="1"/>
+  <c r="O16" i="1"/>
+  <c r="Q16" i="1" s="1"/>
+  <c r="B16" i="1"/>
+  <c r="D16" i="1" s="1"/>
+  <c r="V11" i="1"/>
+  <c r="I11" i="1"/>
+  <c r="H11" i="1"/>
+  <c r="V10" i="1"/>
+  <c r="O15" i="1" s="1"/>
+  <c r="Q15" i="1" s="1"/>
+  <c r="I10" i="1"/>
+  <c r="H10" i="1"/>
+  <c r="V9" i="1"/>
+  <c r="V12" i="1" s="1"/>
+  <c r="I9" i="1"/>
+  <c r="B15" i="1" s="1"/>
+  <c r="D15" i="1" s="1"/>
+  <c r="I17" i="1" s="1"/>
+  <c r="H9" i="1"/>
+  <c r="V8" i="1"/>
+  <c r="I8" i="1"/>
+  <c r="H8" i="1"/>
+  <c r="V17" i="1" l="1"/>
+  <c r="V18" i="1" s="1"/>
+  <c r="O42" i="1"/>
+  <c r="Q42" i="1" s="1"/>
+  <c r="V43" i="1" s="1"/>
+  <c r="J39" i="1"/>
+  <c r="I40" i="1"/>
+  <c r="B43" i="1"/>
+  <c r="D43" i="1" s="1"/>
+  <c r="I43" i="1" s="1"/>
+  <c r="I12" i="1"/>
+  <c r="V38" i="1"/>
+  <c r="I39" i="1"/>
+  <c r="I41" i="1" l="1"/>
+  <c r="I42" i="1"/>
+  <c r="I44" i="1" s="1"/>
+  <c r="V39" i="1"/>
+  <c r="V40" i="1"/>
+  <c r="K13" i="1"/>
+  <c r="I14" i="1" s="1"/>
+  <c r="K15" i="1" l="1"/>
+  <c r="I16" i="1" s="1"/>
+  <c r="I18" i="1" s="1"/>
+  <c r="V41" i="1"/>
+  <c r="V42" i="1" s="1"/>
+  <c r="V44" i="1" s="1"/>
+</calcChain>
+</file>
+
+<file path=xl\drawings\drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>361332</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB83C7B-35E6-4C82-AFAE-46EB8681DC63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="18926175" y="8220075"/>
+          <a:ext cx="447674" cy="532782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444341" cy="562928"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C8E7D6B-B583-4B84-8914-A46038BF547A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="18926175" y="13352144"/>
+          <a:ext cx="444341" cy="562928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>58213</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>142077</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1001233" cy="637954"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="ZoneTexte 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4B1C199-3896-42B6-A850-BD5D7CF5A0CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="58213" y="3742527"/>
+          <a:ext cx="1001233" cy="637954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(2)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425302</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>159488</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1001233" cy="637954"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="ZoneTexte 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBE42E9A-71A1-41B4-B1EE-90ED1CA4EE63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7864327" y="3759938"/>
+          <a:ext cx="1001233" cy="637954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(2)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>44303</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>186069</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1001233" cy="637954"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="ZoneTexte 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8A25816-9DE7-41A4-A1FF-F2D61BA9BCD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44303" y="12539994"/>
+          <a:ext cx="1001233" cy="637954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(2)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>442093</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>165824</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1001233" cy="637954"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="ZoneTexte 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E737FDCE-BFFB-4B16-B834-722B2CDE6BBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7881118" y="12519749"/>
+          <a:ext cx="1001233" cy="637954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="1100"/>
+            <a:t>(2)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="49">
   <si>
     <t xml:space="preserve">CLIENT : BIOARTIGUES  </t>
@@ -214,7 +664,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -1294,381 +1744,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>457199</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>361332</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB83C7B-35E6-4C82-AFAE-46EB8681DC63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="18926175" y="8220075"/>
-          <a:ext cx="447674" cy="532782"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>7619</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="444341" cy="562928"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C8E7D6B-B583-4B84-8914-A46038BF547A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="18926175" y="13352144"/>
-          <a:ext cx="444341" cy="562928"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>58213</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142077</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1001233" cy="637954"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="ZoneTexte 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4B1C199-3896-42B6-A850-BD5D7CF5A0CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="58213" y="3742527"/>
-          <a:ext cx="1001233" cy="637954"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(1)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="fr-FR" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(2)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>425302</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>159488</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1001233" cy="637954"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="ZoneTexte 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBE42E9A-71A1-41B4-B1EE-90ED1CA4EE63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7864327" y="3759938"/>
-          <a:ext cx="1001233" cy="637954"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(1)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="fr-FR" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(2)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>44303</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>186069</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1001233" cy="637954"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="ZoneTexte 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8A25816-9DE7-41A4-A1FF-F2D61BA9BCD2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="44303" y="12539994"/>
-          <a:ext cx="1001233" cy="637954"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(1)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="fr-FR" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(2)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>442093</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>165824</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1001233" cy="637954"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="ZoneTexte 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E737FDCE-BFFB-4B16-B834-722B2CDE6BBB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7881118" y="12519749"/>
-          <a:ext cx="1001233" cy="637954"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(1)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="fr-FR" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="fr-FR" sz="1100"/>
-            <a:t>(2)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1963,7 +2039,41 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nellydoucet\Documents\02. SECRETAIRE COMPTABLE\02. ADMINISTRATION DES VENTES\2023\01. ADMINISTRATION DES VENTES\SC2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9D383AA-420D-416B-A2D6-0E437774B251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{31AA7DA7-77DF-4F79-B56E-8A56121FEEEC}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6B454F-0B21-4808-BC5F-400E7D895E8E}">
   <dimension ref="B2:AMQ1048534"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.85546875" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3629,32 +3739,20 @@
       <c r="W19" s="62"/>
     </row>
     <row r="20" spans="2:1031" s="8" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="113" t="s">
-        <v>31</v>
-      </c>
       <c r="C20" s="114"/>
       <c r="D20" s="114"/>
       <c r="E20" s="114"/>
       <c r="F20" s="115"/>
-      <c r="G20" s="116" t="s">
-        <v>32</v>
-      </c>
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="K20" s="116"/>
       <c r="L20" s="116"/>
       <c r="M20" s="116"/>
-      <c r="O20" s="113" t="s">
-        <v>31</v>
-      </c>
       <c r="P20" s="114"/>
       <c r="Q20" s="114"/>
       <c r="R20" s="114"/>
       <c r="S20" s="115"/>
-      <c r="T20" s="116" t="s">
-        <v>32</v>
-      </c>
       <c r="U20" s="116"/>
       <c r="V20" s="116"/>
       <c r="W20" s="116"/>
@@ -5449,32 +5547,20 @@
       <c r="W45" s="172"/>
     </row>
     <row r="46" spans="2:26" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="113" t="s">
-        <v>31</v>
-      </c>
       <c r="C46" s="114"/>
       <c r="D46" s="114"/>
       <c r="E46" s="114"/>
       <c r="F46" s="115"/>
-      <c r="G46" s="116" t="s">
-        <v>32</v>
-      </c>
       <c r="H46" s="116"/>
       <c r="I46" s="116"/>
       <c r="J46" s="116"/>
       <c r="K46" s="116"/>
       <c r="L46" s="116"/>
       <c r="M46" s="116"/>
-      <c r="O46" s="113" t="s">
-        <v>31</v>
-      </c>
       <c r="P46" s="114"/>
       <c r="Q46" s="114"/>
       <c r="R46" s="114"/>
       <c r="S46" s="115"/>
-      <c r="T46" s="116" t="s">
-        <v>32</v>
-      </c>
       <c r="U46" s="116"/>
       <c r="V46" s="116"/>
       <c r="W46" s="116"/>
